--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/145.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/145.xlsx
@@ -426,13 +426,13 @@
         <v>1.022760544094099</v>
       </c>
       <c r="E2">
-        <v>-20.03507603429913</v>
+        <v>-21.37692628140797</v>
       </c>
       <c r="F2">
-        <v>-1.098281127840399</v>
+        <v>-1.087824646114861</v>
       </c>
       <c r="G2">
-        <v>-8.69876743583853</v>
+        <v>-10.85287320733151</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>1.095346188240879</v>
       </c>
       <c r="E3">
-        <v>-19.84847120586506</v>
+        <v>-20.07529794043526</v>
       </c>
       <c r="F3">
-        <v>-1.197757284140383</v>
+        <v>-1.016483160283559</v>
       </c>
       <c r="G3">
-        <v>-8.689391970871315</v>
+        <v>-9.065966525963411</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>1.275820029569154</v>
       </c>
       <c r="E4">
-        <v>-18.76199519347078</v>
+        <v>-20.2942360732841</v>
       </c>
       <c r="F4">
-        <v>-1.031277802097558</v>
+        <v>-1.251672404918992</v>
       </c>
       <c r="G4">
-        <v>-8.088915289321688</v>
+        <v>-10.10160779755916</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>1.55831464769521</v>
       </c>
       <c r="E5">
-        <v>-19.7690281863485</v>
+        <v>-21.07354116526409</v>
       </c>
       <c r="F5">
-        <v>-1.168210247249927</v>
+        <v>-1.365093298077703</v>
       </c>
       <c r="G5">
-        <v>-8.797415071817733</v>
+        <v>-10.14142703930551</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>1.938011493254234</v>
       </c>
       <c r="E6">
-        <v>-19.94264987980258</v>
+        <v>-21.67994459115722</v>
       </c>
       <c r="F6">
-        <v>-1.04397833111728</v>
+        <v>-1.431888703602441</v>
       </c>
       <c r="G6">
-        <v>-9.355609465739787</v>
+        <v>-9.518518101181783</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>2.404539375744948</v>
       </c>
       <c r="E7">
-        <v>-21.06353323770714</v>
+        <v>-22.60161132051635</v>
       </c>
       <c r="F7">
-        <v>-0.7258173223152402</v>
+        <v>-1.31488760652883</v>
       </c>
       <c r="G7">
-        <v>-9.058176812309506</v>
+        <v>-9.304779349529817</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>2.949803553087109</v>
       </c>
       <c r="E8">
-        <v>-20.71190175948555</v>
+        <v>-23.80625333366678</v>
       </c>
       <c r="F8">
-        <v>-1.015886735753543</v>
+        <v>-1.405135749961628</v>
       </c>
       <c r="G8">
-        <v>-9.187840949446141</v>
+        <v>-10.01262695455462</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.567080160043916</v>
       </c>
       <c r="E9">
-        <v>-22.60265286953811</v>
+        <v>-23.86207130428532</v>
       </c>
       <c r="F9">
-        <v>-1.043689230893703</v>
+        <v>-1.109382079405315</v>
       </c>
       <c r="G9">
-        <v>-7.114178124011915</v>
+        <v>-9.413937967596206</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.249166675087979</v>
       </c>
       <c r="E10">
-        <v>-22.69207211729357</v>
+        <v>-23.99537599364912</v>
       </c>
       <c r="F10">
-        <v>-1.045766776339924</v>
+        <v>-1.323488545272097</v>
       </c>
       <c r="G10">
-        <v>-8.917084671971308</v>
+        <v>-9.032119508369902</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.988347957767219</v>
       </c>
       <c r="E11">
-        <v>-23.23936537196458</v>
+        <v>-25.90292774227014</v>
       </c>
       <c r="F11">
-        <v>-1.094352181248921</v>
+        <v>-1.643850526263376</v>
       </c>
       <c r="G11">
-        <v>-9.21796360330797</v>
+        <v>-8.171486916162189</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.776047806441222</v>
       </c>
       <c r="E12">
-        <v>-23.72712730733075</v>
+        <v>-25.75199823206849</v>
       </c>
       <c r="F12">
-        <v>-1.244474720556067</v>
+        <v>-1.494640847834114</v>
       </c>
       <c r="G12">
-        <v>-7.46596331410595</v>
+        <v>-7.698366921508327</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>6.600399540987829</v>
       </c>
       <c r="E13">
-        <v>-25.33816363487754</v>
+        <v>-25.70225747356824</v>
       </c>
       <c r="F13">
-        <v>-1.11025932048488</v>
+        <v>-1.571248265245013</v>
       </c>
       <c r="G13">
-        <v>-6.87400466622887</v>
+        <v>-7.446960782710534</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>7.443740331659313</v>
       </c>
       <c r="E14">
-        <v>-25.30581674504075</v>
+        <v>-27.01181517252838</v>
       </c>
       <c r="F14">
-        <v>-0.7865548770233055</v>
+        <v>-1.3076882654311</v>
       </c>
       <c r="G14">
-        <v>-6.746922754612867</v>
+        <v>-7.351660108271535</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>8.282292429927535</v>
       </c>
       <c r="E15">
-        <v>-27.23504177026248</v>
+        <v>-27.88025421840135</v>
       </c>
       <c r="F15">
-        <v>-1.107340982124817</v>
+        <v>-0.9146461568855959</v>
       </c>
       <c r="G15">
-        <v>-6.160479475604212</v>
+        <v>-7.18479206036457</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>9.093736950534709</v>
       </c>
       <c r="E16">
-        <v>-26.35975114321591</v>
+        <v>-28.93074697633068</v>
       </c>
       <c r="F16">
-        <v>-1.13802950929633</v>
+        <v>-0.6656554829521205</v>
       </c>
       <c r="G16">
-        <v>-5.165700267599691</v>
+        <v>-6.4112698529317</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>9.851573153339876</v>
       </c>
       <c r="E17">
-        <v>-27.75342977534253</v>
+        <v>-29.3925607556329</v>
       </c>
       <c r="F17">
-        <v>-0.8003074326445829</v>
+        <v>-1.065781789526366</v>
       </c>
       <c r="G17">
-        <v>-4.495771651181695</v>
+        <v>-5.998040937628792</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>10.53134846998717</v>
       </c>
       <c r="E18">
-        <v>-28.6299612042672</v>
+        <v>-29.81124082001206</v>
       </c>
       <c r="F18">
-        <v>-1.260676758587422</v>
+        <v>-0.9352683633782896</v>
       </c>
       <c r="G18">
-        <v>-4.186742156727347</v>
+        <v>-6.034483422925089</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>11.11375715382082</v>
       </c>
       <c r="E19">
-        <v>-29.69486130225194</v>
+        <v>-31.24791504860451</v>
       </c>
       <c r="F19">
-        <v>-1.029518349734012</v>
+        <v>-0.6118994087148494</v>
       </c>
       <c r="G19">
-        <v>-3.911877492238279</v>
+        <v>-5.527665385226984</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>11.5850378797615</v>
       </c>
       <c r="E20">
-        <v>-30.18251455424193</v>
+        <v>-31.80114286846257</v>
       </c>
       <c r="F20">
-        <v>-1.008256643606357</v>
+        <v>-0.6955247547622651</v>
       </c>
       <c r="G20">
-        <v>-3.485456052961375</v>
+        <v>-5.018606108198793</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>11.93961521470891</v>
       </c>
       <c r="E21">
-        <v>-30.70815943891927</v>
+        <v>-32.39558885873845</v>
       </c>
       <c r="F21">
-        <v>-0.7388177203347757</v>
+        <v>-0.1108332206398732</v>
       </c>
       <c r="G21">
-        <v>-3.667903528176149</v>
+        <v>-4.448301738694085</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>12.17447853209364</v>
       </c>
       <c r="E22">
-        <v>-31.51685432720904</v>
+        <v>-32.84222998587797</v>
       </c>
       <c r="F22">
-        <v>-0.8748936335926504</v>
+        <v>-0.3442240796438283</v>
       </c>
       <c r="G22">
-        <v>-3.2192484650575</v>
+        <v>-4.300346837452977</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>12.29890410055688</v>
       </c>
       <c r="E23">
-        <v>-31.53458330294907</v>
+        <v>-33.65746851910882</v>
       </c>
       <c r="F23">
-        <v>-0.2001883840124531</v>
+        <v>-0.5836346845639274</v>
       </c>
       <c r="G23">
-        <v>-2.67057520010639</v>
+        <v>-4.722716168989813</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>12.32337769510129</v>
       </c>
       <c r="E24">
-        <v>-33.07306215570796</v>
+        <v>-34.15006007200418</v>
       </c>
       <c r="F24">
-        <v>-0.4447994794873275</v>
+        <v>-0.3201492378162663</v>
       </c>
       <c r="G24">
-        <v>-2.591330671532856</v>
+        <v>-3.519352728737973</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>12.2610457492194</v>
       </c>
       <c r="E25">
-        <v>-32.56110684795581</v>
+        <v>-34.54121154289071</v>
       </c>
       <c r="F25">
-        <v>-0.7247661240810876</v>
+        <v>-0.02140930277286097</v>
       </c>
       <c r="G25">
-        <v>-2.831020789667168</v>
+        <v>-4.704124145241266</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>12.12586852453134</v>
       </c>
       <c r="E26">
-        <v>-31.87836240724137</v>
+        <v>-33.80302725913737</v>
       </c>
       <c r="F26">
-        <v>-0.6909355993507558</v>
+        <v>-0.5670557393642981</v>
       </c>
       <c r="G26">
-        <v>-3.554626591458907</v>
+        <v>-3.992936199767334</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>11.92943591242025</v>
       </c>
       <c r="E27">
-        <v>-32.93252096487991</v>
+        <v>-35.64361872684398</v>
       </c>
       <c r="F27">
-        <v>-0.6684595066105968</v>
+        <v>-0.1886152630279412</v>
       </c>
       <c r="G27">
-        <v>-3.318240397772787</v>
+        <v>-4.194776850751158</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>11.68524884027695</v>
       </c>
       <c r="E28">
-        <v>-31.89126176545222</v>
+        <v>-34.25669657793681</v>
       </c>
       <c r="F28">
-        <v>-0.4358920448050244</v>
+        <v>-0.2469364700220404</v>
       </c>
       <c r="G28">
-        <v>-1.877464494717652</v>
+        <v>-4.497390507950398</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>11.40251282400487</v>
       </c>
       <c r="E29">
-        <v>-33.78010865218456</v>
+        <v>-33.1467653344198</v>
       </c>
       <c r="F29">
-        <v>-0.02955712454679691</v>
+        <v>-0.06172097406269612</v>
       </c>
       <c r="G29">
-        <v>-4.056756896673404</v>
+        <v>-4.245865189513192</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>11.09291785320159</v>
       </c>
       <c r="E30">
-        <v>-32.3838102978445</v>
+        <v>-34.94826248601818</v>
       </c>
       <c r="F30">
-        <v>0.3048929008638923</v>
+        <v>-0.4341549583613538</v>
       </c>
       <c r="G30">
-        <v>-2.127238534564585</v>
+        <v>-4.694182576986835</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>10.76440030340938</v>
       </c>
       <c r="E31">
-        <v>-32.77911211515907</v>
+        <v>-33.52374268166232</v>
       </c>
       <c r="F31">
-        <v>0.1210135615252636</v>
+        <v>0.00591191090627232</v>
       </c>
       <c r="G31">
-        <v>-3.311268388867082</v>
+        <v>-4.414911576384997</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>10.42347935844513</v>
       </c>
       <c r="E32">
-        <v>-31.74819595036489</v>
+        <v>-31.76903598774819</v>
       </c>
       <c r="F32">
-        <v>-0.4857473369425127</v>
+        <v>-0.02457697972116629</v>
       </c>
       <c r="G32">
-        <v>-3.830848579619077</v>
+        <v>-5.367719688042636</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>10.07532368853769</v>
       </c>
       <c r="E33">
-        <v>-31.10245819924113</v>
+        <v>-32.79551198377784</v>
       </c>
       <c r="F33">
-        <v>-0.2325560119094409</v>
+        <v>-0.1978971197763096</v>
       </c>
       <c r="G33">
-        <v>-3.614411733352605</v>
+        <v>-5.489057803148004</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>9.722610063067687</v>
       </c>
       <c r="E34">
-        <v>-31.08181062200316</v>
+        <v>-32.76467986849661</v>
       </c>
       <c r="F34">
-        <v>0.03933156540481558</v>
+        <v>-0.5874700256388892</v>
       </c>
       <c r="G34">
-        <v>-4.703710327048857</v>
+        <v>-5.303663942403278</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>9.368952141125336</v>
       </c>
       <c r="E35">
-        <v>-29.48485105590922</v>
+        <v>-31.53577429161309</v>
       </c>
       <c r="F35">
-        <v>0.4217341230287626</v>
+        <v>0.3537591223224379</v>
       </c>
       <c r="G35">
-        <v>-4.881946788337679</v>
+        <v>-5.81739770973292</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>9.019316941301534</v>
       </c>
       <c r="E36">
-        <v>-30.36577736885834</v>
+        <v>-30.90407933838712</v>
       </c>
       <c r="F36">
-        <v>0.06383798664923615</v>
+        <v>0.1474964673927638</v>
       </c>
       <c r="G36">
-        <v>-5.30242910891713</v>
+        <v>-5.220112394083152</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>8.677384212586817</v>
       </c>
       <c r="E37">
-        <v>-29.29752167163392</v>
+        <v>-30.16567768788141</v>
       </c>
       <c r="F37">
-        <v>0.3264105725190122</v>
+        <v>-0.1596936435265992</v>
       </c>
       <c r="G37">
-        <v>-4.938305515598231</v>
+        <v>-6.391115251688618</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>8.346724748582279</v>
       </c>
       <c r="E38">
-        <v>-28.56778525614189</v>
+        <v>-29.49322873282341</v>
       </c>
       <c r="F38">
-        <v>0.3657398000691272</v>
+        <v>0.07988180650665697</v>
       </c>
       <c r="G38">
-        <v>-5.769633158692316</v>
+        <v>-5.676891535955173</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>8.029910493577438</v>
       </c>
       <c r="E39">
-        <v>-27.31409534101438</v>
+        <v>-28.55765958826074</v>
       </c>
       <c r="F39">
-        <v>0.8319681686519673</v>
+        <v>0.3709684551155977</v>
       </c>
       <c r="G39">
-        <v>-5.257912203050551</v>
+        <v>-7.0127728035985</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>7.729658830790868</v>
       </c>
       <c r="E40">
-        <v>-28.42791880794098</v>
+        <v>-27.57690985852354</v>
       </c>
       <c r="F40">
-        <v>0.784282370742411</v>
+        <v>0.4773034935107618</v>
       </c>
       <c r="G40">
-        <v>-5.514082216879355</v>
+        <v>-6.743062658514076</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>7.447538255995631</v>
       </c>
       <c r="E41">
-        <v>-25.76436549458344</v>
+        <v>-27.63576190672723</v>
       </c>
       <c r="F41">
-        <v>0.8202434564327431</v>
+        <v>0.5751626766404814</v>
       </c>
       <c r="G41">
-        <v>-5.309056821086751</v>
+        <v>-5.9978224416232</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>7.183336149743175</v>
       </c>
       <c r="E42">
-        <v>-26.48679295302709</v>
+        <v>-27.50419615138238</v>
       </c>
       <c r="F42">
-        <v>1.112556088797827</v>
+        <v>0.6669242473181938</v>
       </c>
       <c r="G42">
-        <v>-6.072180604980771</v>
+        <v>-7.133217071408264</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.94127011920385</v>
       </c>
       <c r="E43">
-        <v>-25.92535274555612</v>
+        <v>-26.9318287361309</v>
       </c>
       <c r="F43">
-        <v>0.7162170779891812</v>
+        <v>0.244667277210757</v>
       </c>
       <c r="G43">
-        <v>-6.202824663597029</v>
+        <v>-6.688283061475756</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.721222113826509</v>
       </c>
       <c r="E44">
-        <v>-25.26326720326468</v>
+        <v>-26.01716755606164</v>
       </c>
       <c r="F44">
-        <v>1.367380125981817</v>
+        <v>1.067753009450013</v>
       </c>
       <c r="G44">
-        <v>-5.996388975404696</v>
+        <v>-6.830156490561222</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.524050048595468</v>
       </c>
       <c r="E45">
-        <v>-23.62907678811668</v>
+        <v>-24.9417546056681</v>
       </c>
       <c r="F45">
-        <v>0.8268770225943616</v>
+        <v>0.8808766368480557</v>
       </c>
       <c r="G45">
-        <v>-6.009535151741142</v>
+        <v>-6.491143385157696</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.348823891530767</v>
       </c>
       <c r="E46">
-        <v>-23.33929973636585</v>
+        <v>-24.55584257920844</v>
       </c>
       <c r="F46">
-        <v>1.366412592855347</v>
+        <v>1.294902948441277</v>
       </c>
       <c r="G46">
-        <v>-7.237879968632323</v>
+        <v>-7.228160206929022</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.193733170149173</v>
       </c>
       <c r="E47">
-        <v>-21.88877064154693</v>
+        <v>-23.3267558633646</v>
       </c>
       <c r="F47">
-        <v>1.514730119591793</v>
+        <v>1.205860079579552</v>
       </c>
       <c r="G47">
-        <v>-8.232831325004886</v>
+        <v>-7.418619202348833</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.055912522580654</v>
       </c>
       <c r="E48">
-        <v>-21.11186564079101</v>
+        <v>-23.9966620802673</v>
       </c>
       <c r="F48">
-        <v>1.900358339882241</v>
+        <v>1.504624037277639</v>
       </c>
       <c r="G48">
-        <v>-7.068035740285554</v>
+        <v>-7.181680147557655</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.929307284242251</v>
       </c>
       <c r="E49">
-        <v>-21.07414798078112</v>
+        <v>-21.93649622911377</v>
       </c>
       <c r="F49">
-        <v>1.915635091524669</v>
+        <v>1.474213013186063</v>
       </c>
       <c r="G49">
-        <v>-7.133710342693615</v>
+        <v>-6.962995440870018</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.812587678572104</v>
       </c>
       <c r="E50">
-        <v>-19.78387705261965</v>
+        <v>-21.34818858535529</v>
       </c>
       <c r="F50">
-        <v>1.830773821312277</v>
+        <v>1.416881705238309</v>
       </c>
       <c r="G50">
-        <v>-7.41372621604179</v>
+        <v>-6.849946931794986</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.700189667002389</v>
       </c>
       <c r="E51">
-        <v>-19.87560129364502</v>
+        <v>-20.17150989920223</v>
       </c>
       <c r="F51">
-        <v>1.853085068939279</v>
+        <v>2.169274563322656</v>
       </c>
       <c r="G51">
-        <v>-7.027190229422026</v>
+        <v>-7.31297969419069</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>5.588264191580352</v>
       </c>
       <c r="E52">
-        <v>-19.24504298739497</v>
+        <v>-19.46505889705764</v>
       </c>
       <c r="F52">
-        <v>2.12648607349845</v>
+        <v>1.711609856949957</v>
       </c>
       <c r="G52">
-        <v>-7.650559333375712</v>
+        <v>-8.069439349914155</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>5.472279680101727</v>
       </c>
       <c r="E53">
-        <v>-17.73006465049889</v>
+        <v>-19.21342518187342</v>
       </c>
       <c r="F53">
-        <v>2.09934047370871</v>
+        <v>1.77798362346667</v>
       </c>
       <c r="G53">
-        <v>-8.05742869069768</v>
+        <v>-7.941334479726518</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>5.348577459208308</v>
       </c>
       <c r="E54">
-        <v>-17.74691963075544</v>
+        <v>-19.15253079189227</v>
       </c>
       <c r="F54">
-        <v>2.135846625150084</v>
+        <v>1.735491689172666</v>
       </c>
       <c r="G54">
-        <v>-6.714479408328009</v>
+        <v>-8.516048495889535</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>5.214965464261122</v>
       </c>
       <c r="E55">
-        <v>-17.54937853759284</v>
+        <v>-19.16272891535755</v>
       </c>
       <c r="F55">
-        <v>2.063927767239031</v>
+        <v>1.557145844084739</v>
       </c>
       <c r="G55">
-        <v>-7.683621751676413</v>
+        <v>-7.531929244521468</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>5.069214245948318</v>
       </c>
       <c r="E56">
-        <v>-16.38910198429556</v>
+        <v>-18.77934830586818</v>
       </c>
       <c r="F56">
-        <v>1.743394314195374</v>
+        <v>1.75397753613354</v>
       </c>
       <c r="G56">
-        <v>-7.157135762929498</v>
+        <v>-8.731776885410603</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>4.913874810360307</v>
       </c>
       <c r="E57">
-        <v>-15.60208490108051</v>
+        <v>-18.59983506773012</v>
       </c>
       <c r="F57">
-        <v>2.160903082349964</v>
+        <v>2.028846407730472</v>
       </c>
       <c r="G57">
-        <v>-7.826534692061212</v>
+        <v>-8.502647407546565</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>4.750646264817032</v>
       </c>
       <c r="E58">
-        <v>-14.69573799928933</v>
+        <v>-17.64970687923278</v>
       </c>
       <c r="F58">
-        <v>2.245809084402107</v>
+        <v>1.46305656100516</v>
       </c>
       <c r="G58">
-        <v>-7.234546249274277</v>
+        <v>-8.677970588760829</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>4.583847794595006</v>
       </c>
       <c r="E59">
-        <v>-15.60186753432814</v>
+        <v>-16.7182677029651</v>
       </c>
       <c r="F59">
-        <v>1.863567230054304</v>
+        <v>1.647525697934581</v>
       </c>
       <c r="G59">
-        <v>-7.876431234429107</v>
+        <v>-8.965229935748928</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>4.417322176473676</v>
       </c>
       <c r="E60">
-        <v>-14.09946929822537</v>
+        <v>-16.23768339890109</v>
       </c>
       <c r="F60">
-        <v>1.766794036589654</v>
+        <v>1.83422479991234</v>
       </c>
       <c r="G60">
-        <v>-7.174463158282044</v>
+        <v>-8.529389994412798</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>4.254722152859963</v>
       </c>
       <c r="E61">
-        <v>-14.0440543617935</v>
+        <v>-16.3311511024194</v>
       </c>
       <c r="F61">
-        <v>1.461305392315641</v>
+        <v>1.324444186759913</v>
       </c>
       <c r="G61">
-        <v>-7.634188685684016</v>
+        <v>-8.958608844670387</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>4.099635593809777</v>
       </c>
       <c r="E62">
-        <v>-14.54757991518038</v>
+        <v>-16.7567008618682</v>
       </c>
       <c r="F62">
-        <v>1.557563341255749</v>
+        <v>1.035983462817846</v>
       </c>
       <c r="G62">
-        <v>-7.308785232992433</v>
+        <v>-9.192548545202985</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>3.954267293487693</v>
       </c>
       <c r="E63">
-        <v>-14.00721522574111</v>
+        <v>-15.94931923104065</v>
       </c>
       <c r="F63">
-        <v>1.549360847233229</v>
+        <v>1.262197346643946</v>
       </c>
       <c r="G63">
-        <v>-8.527949907103215</v>
+        <v>-8.762892702934213</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>3.822071447587635</v>
       </c>
       <c r="E64">
-        <v>-13.65637170199685</v>
+        <v>-15.26978094992365</v>
       </c>
       <c r="F64">
-        <v>1.030623925721734</v>
+        <v>1.415581168415914</v>
       </c>
       <c r="G64">
-        <v>-7.733958596601032</v>
+        <v>-9.283956018087801</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>3.704941670735774</v>
       </c>
       <c r="E65">
-        <v>-12.98075960784449</v>
+        <v>-14.18542426336496</v>
       </c>
       <c r="F65">
-        <v>0.7756971709797968</v>
+        <v>1.041811855863944</v>
       </c>
       <c r="G65">
-        <v>-7.790545751503794</v>
+        <v>-8.798765774397756</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>3.604587515497262</v>
       </c>
       <c r="E66">
-        <v>-13.60924387299902</v>
+        <v>-15.15361200620488</v>
       </c>
       <c r="F66">
-        <v>0.8770678035299836</v>
+        <v>0.6423797211732445</v>
       </c>
       <c r="G66">
-        <v>-7.679069751559916</v>
+        <v>-9.368394792612452</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>3.521401593037496</v>
       </c>
       <c r="E67">
-        <v>-12.72558915446028</v>
+        <v>-15.05168058476623</v>
       </c>
       <c r="F67">
-        <v>0.6418247150133688</v>
+        <v>0.6406550602406159</v>
       </c>
       <c r="G67">
-        <v>-7.819751384251244</v>
+        <v>-8.555175833618181</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>3.454659711927774</v>
       </c>
       <c r="E68">
-        <v>-11.50596694929248</v>
+        <v>-13.6833840494526</v>
       </c>
       <c r="F68">
-        <v>0.7520986404088446</v>
+        <v>0.7654883711076957</v>
       </c>
       <c r="G68">
-        <v>-7.664582804280065</v>
+        <v>-9.485247118512108</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>3.40311477009893</v>
       </c>
       <c r="E69">
-        <v>-11.07785407355534</v>
+        <v>-15.27026096816846</v>
       </c>
       <c r="F69">
-        <v>0.5406727714575211</v>
+        <v>0.1414029967777707</v>
       </c>
       <c r="G69">
-        <v>-7.890348767876203</v>
+        <v>-8.549465142562939</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>3.364606847517754</v>
       </c>
       <c r="E70">
-        <v>-12.92853271711403</v>
+        <v>-13.37200164821118</v>
       </c>
       <c r="F70">
-        <v>0.9490877222641783</v>
+        <v>-0.1631379951874396</v>
       </c>
       <c r="G70">
-        <v>-8.066582349113766</v>
+        <v>-8.667393395762858</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>3.337164313478544</v>
       </c>
       <c r="E71">
-        <v>-13.31554063428354</v>
+        <v>-14.14403401093485</v>
       </c>
       <c r="F71">
-        <v>0.2848530366553667</v>
+        <v>0.1394116015414406</v>
       </c>
       <c r="G71">
-        <v>-8.094182367274669</v>
+        <v>-8.719683462555645</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>3.319407765702532</v>
       </c>
       <c r="E72">
-        <v>-12.68595594994515</v>
+        <v>-14.188399470788</v>
       </c>
       <c r="F72">
-        <v>-0.2410252402356631</v>
+        <v>-0.01319189813708988</v>
       </c>
       <c r="G72">
-        <v>-7.832771759857198</v>
+        <v>-8.032612841335304</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>3.309666211376916</v>
       </c>
       <c r="E73">
-        <v>-13.22256653443206</v>
+        <v>-13.99941266502589</v>
       </c>
       <c r="F73">
-        <v>-0.2405862055121794</v>
+        <v>-0.06668869337728475</v>
       </c>
       <c r="G73">
-        <v>-7.833039914045879</v>
+        <v>-8.54214221583007</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>3.307102418998173</v>
       </c>
       <c r="E74">
-        <v>-12.59018778163094</v>
+        <v>-13.4746802678611</v>
       </c>
       <c r="F74">
-        <v>-0.3205567945784437</v>
+        <v>0.3852503375072639</v>
       </c>
       <c r="G74">
-        <v>-7.785427648100081</v>
+        <v>-8.109914079677285</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.311312947312947</v>
       </c>
       <c r="E75">
-        <v>-12.75763263653856</v>
+        <v>-15.12762762234887</v>
       </c>
       <c r="F75">
-        <v>0.5245974736387939</v>
+        <v>-0.3678259236843918</v>
       </c>
       <c r="G75">
-        <v>-6.463622820089735</v>
+        <v>-7.900949134692949</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.322874039393374</v>
       </c>
       <c r="E76">
-        <v>-12.53009493154915</v>
+        <v>-15.08344782993004</v>
       </c>
       <c r="F76">
-        <v>-0.0476768331156333</v>
+        <v>-0.5209612352355196</v>
       </c>
       <c r="G76">
-        <v>-7.077119877245314</v>
+        <v>-8.373810906794748</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.343002324142816</v>
       </c>
       <c r="E77">
-        <v>-12.21891631163808</v>
+        <v>-15.34305618784176</v>
       </c>
       <c r="F77">
-        <v>-0.3909108664656085</v>
+        <v>-0.5940663152673816</v>
       </c>
       <c r="G77">
-        <v>-6.031023902836551</v>
+        <v>-6.819496533924769</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.372549043805297</v>
       </c>
       <c r="E78">
-        <v>-13.1728755891459</v>
+        <v>-14.9938655571103</v>
       </c>
       <c r="F78">
-        <v>-0.1105805685820194</v>
+        <v>-1.099449954245749</v>
       </c>
       <c r="G78">
-        <v>-6.44211089517555</v>
+        <v>-8.067234526585001</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.413992229312848</v>
       </c>
       <c r="E79">
-        <v>-13.48116957111409</v>
+        <v>-15.96072192859197</v>
       </c>
       <c r="F79">
-        <v>-0.954999246545571</v>
+        <v>-0.8187576598071363</v>
       </c>
       <c r="G79">
-        <v>-5.749849338549631</v>
+        <v>-7.236794109695442</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.467932008164083</v>
       </c>
       <c r="E80">
-        <v>-14.56989170661617</v>
+        <v>-16.76715257987791</v>
       </c>
       <c r="F80">
-        <v>-0.5615131330721667</v>
+        <v>-0.9168570694836677</v>
       </c>
       <c r="G80">
-        <v>-5.44733168717103</v>
+        <v>-7.461295444895578</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.535735788348307</v>
       </c>
       <c r="E81">
-        <v>-15.24252406487148</v>
+        <v>-15.46919683132542</v>
       </c>
       <c r="F81">
-        <v>-1.010493235593916</v>
+        <v>-0.6104050339201991</v>
       </c>
       <c r="G81">
-        <v>-5.562853173763898</v>
+        <v>-6.622482658337202</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.616869334084649</v>
       </c>
       <c r="E82">
-        <v>-14.5945266052179</v>
+        <v>-16.62164365306344</v>
       </c>
       <c r="F82">
-        <v>-0.6274793428267025</v>
+        <v>-0.5820052858826208</v>
       </c>
       <c r="G82">
-        <v>-5.452449790574743</v>
+        <v>-6.731836598590408</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.709673261421839</v>
       </c>
       <c r="E83">
-        <v>-15.72837951268042</v>
+        <v>-17.37414017891803</v>
       </c>
       <c r="F83">
-        <v>-0.6963746597175373</v>
+        <v>-0.99016344279441</v>
       </c>
       <c r="G83">
-        <v>-5.280496744719459</v>
+        <v>-6.843762832727627</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.811537355232559</v>
       </c>
       <c r="E84">
-        <v>-16.48495166514191</v>
+        <v>-18.58552961833988</v>
       </c>
       <c r="F84">
-        <v>-1.194744511896401</v>
+        <v>-1.018009841406918</v>
       </c>
       <c r="G84">
-        <v>-4.945317251050408</v>
+        <v>-5.689435193003471</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.918491718920662</v>
       </c>
       <c r="E85">
-        <v>-17.03885196339011</v>
+        <v>-18.93778602597454</v>
       </c>
       <c r="F85">
-        <v>-1.026633146070061</v>
+        <v>-1.130104518353747</v>
       </c>
       <c r="G85">
-        <v>-4.981130732694243</v>
+        <v>-5.659249638776396</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.02786554358479</v>
       </c>
       <c r="E86">
-        <v>-17.62134051804874</v>
+        <v>-20.39979933087691</v>
       </c>
       <c r="F86">
-        <v>-1.393724160620662</v>
+        <v>-0.9281236945291438</v>
       </c>
       <c r="G86">
-        <v>-5.433874319553893</v>
+        <v>-5.836234713851374</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.134422432679647</v>
       </c>
       <c r="E87">
-        <v>-18.47242645152431</v>
+        <v>-21.33736553247696</v>
       </c>
       <c r="F87">
-        <v>-1.179801592317301</v>
+        <v>-1.494084184939433</v>
       </c>
       <c r="G87">
-        <v>-4.837188212646732</v>
+        <v>-5.502134458028126</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.234860462766849</v>
       </c>
       <c r="E88">
-        <v>-20.83338713168932</v>
+        <v>-21.09209432327352</v>
       </c>
       <c r="F88">
-        <v>-1.53683456986311</v>
+        <v>-1.473246602922012</v>
       </c>
       <c r="G88">
-        <v>-6.030110192267712</v>
+        <v>-6.513469704274541</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.324481916315455</v>
       </c>
       <c r="E89">
-        <v>-20.46881780322781</v>
+        <v>-24.04228645589457</v>
       </c>
       <c r="F89">
-        <v>-1.301056356004287</v>
+        <v>-1.450235384839644</v>
       </c>
       <c r="G89">
-        <v>-4.272058225819905</v>
+        <v>-5.868621780862064</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.39863835064684</v>
       </c>
       <c r="E90">
-        <v>-22.003345562415</v>
+        <v>-23.60334599880509</v>
       </c>
       <c r="F90">
-        <v>-1.433848620877464</v>
+        <v>-1.480223941555792</v>
       </c>
       <c r="G90">
-        <v>-4.009528654010161</v>
+        <v>-5.502680698042105</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.452950504528757</v>
       </c>
       <c r="E91">
-        <v>-23.37442258076934</v>
+        <v>-25.85311905665977</v>
       </c>
       <c r="F91">
-        <v>-1.567644867042835</v>
+        <v>-1.482615438247674</v>
       </c>
       <c r="G91">
-        <v>-5.138471030539185</v>
+        <v>-5.760774138829226</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.482558273047078</v>
       </c>
       <c r="E92">
-        <v>-24.73351725689938</v>
+        <v>-28.57610406289398</v>
       </c>
       <c r="F92">
-        <v>-1.396085836086043</v>
+        <v>-1.900201244570724</v>
       </c>
       <c r="G92">
-        <v>-5.710738553548682</v>
+        <v>-6.103687066878014</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.48448761130122</v>
       </c>
       <c r="E93">
-        <v>-27.23766375671292</v>
+        <v>-28.79734266053872</v>
       </c>
       <c r="F93">
-        <v>-1.743141128265133</v>
+        <v>-2.222760055914227</v>
       </c>
       <c r="G93">
-        <v>-5.470349910305583</v>
+        <v>-6.265311210650773</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.454704410649455</v>
       </c>
       <c r="E94">
-        <v>-29.15820769726195</v>
+        <v>-29.93757165940404</v>
       </c>
       <c r="F94">
-        <v>-2.021031055780075</v>
+        <v>-2.642779605666702</v>
       </c>
       <c r="G94">
-        <v>-5.627134036499926</v>
+        <v>-6.764915569618806</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.392345081918765</v>
       </c>
       <c r="E95">
-        <v>-30.93201096606643</v>
+        <v>-30.60841753466333</v>
       </c>
       <c r="F95">
-        <v>-2.101825870412124</v>
+        <v>-2.497416037088639</v>
       </c>
       <c r="G95">
-        <v>-5.004079434372471</v>
+        <v>-6.459014540699069</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.294821725491615</v>
       </c>
       <c r="E96">
-        <v>-32.16648656597939</v>
+        <v>-33.01612791624652</v>
       </c>
       <c r="F96">
-        <v>-2.346494123237792</v>
+        <v>-2.293602864569043</v>
       </c>
       <c r="G96">
-        <v>-5.787553141696391</v>
+        <v>-7.278205723846185</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.164439709831586</v>
       </c>
       <c r="E97">
-        <v>-34.06174577190659</v>
+        <v>-35.31848561427827</v>
       </c>
       <c r="F97">
-        <v>-2.35902483693994</v>
+        <v>-2.457657715223874</v>
       </c>
       <c r="G97">
-        <v>-5.391721143202353</v>
+        <v>-6.516138003979194</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.99873782772313</v>
       </c>
       <c r="E98">
-        <v>-35.28525567200998</v>
+        <v>-36.68763803117935</v>
       </c>
       <c r="F98">
-        <v>-2.306702666676915</v>
+        <v>-3.168007614146534</v>
       </c>
       <c r="G98">
-        <v>-6.851310876557165</v>
+        <v>-7.29776111634666</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.805963852090042</v>
       </c>
       <c r="E99">
-        <v>-38.03862447459866</v>
+        <v>-39.44430809131961</v>
       </c>
       <c r="F99">
-        <v>-2.595951168019043</v>
+        <v>-3.261157528591339</v>
       </c>
       <c r="G99">
-        <v>-6.777055340111313</v>
+        <v>-8.034526336657002</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.580606334881313</v>
       </c>
       <c r="E100">
-        <v>-41.12094615757852</v>
+        <v>-41.87647449678123</v>
       </c>
       <c r="F100">
-        <v>-2.259958722504341</v>
+        <v>-3.198778149690924</v>
       </c>
       <c r="G100">
-        <v>-6.730658044378427</v>
+        <v>-7.207012442024158</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.342303202287064</v>
       </c>
       <c r="E101">
-        <v>-42.41012572350413</v>
+        <v>-43.02876055769198</v>
       </c>
       <c r="F101">
-        <v>-2.778256609292353</v>
+        <v>-3.431226326590494</v>
       </c>
       <c r="G101">
-        <v>-6.935537776167303</v>
+        <v>-7.638187824695455</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.0701369492267</v>
       </c>
       <c r="E102">
-        <v>-45.01158686550551</v>
+        <v>-45.44536712646325</v>
       </c>
       <c r="F102">
-        <v>-3.220623854837553</v>
+        <v>-4.016152288687878</v>
       </c>
       <c r="G102">
-        <v>-7.437522417378072</v>
+        <v>-8.689239685776508</v>
       </c>
     </row>
   </sheetData>
